--- a/גדות סקיי - מחירון 46.xlsx
+++ b/גדות סקיי - מחירון 46.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Windows.old\Users\Public\VUE\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD9E6A3F-252D-42CA-90F1-AC4283A15ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1154DF1B-A0B3-4FD3-9EAF-5AA61AB735CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{025406CF-A7AE-4DE8-B584-23F180A0A057}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{025406CF-A7AE-4DE8-B584-23F180A0A057}"/>
   </bookViews>
   <sheets>
     <sheet name="price" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="35">
   <si>
     <t>צפון דרום מערב</t>
   </si>
@@ -93,20 +93,68 @@
     <t>balconyArea</t>
   </si>
   <si>
-    <t>eqvivalentArea</t>
-  </si>
-  <si>
     <t>flatPrice</t>
   </si>
   <si>
     <t>status</t>
+  </si>
+  <si>
+    <t>equivalentArea</t>
+  </si>
+  <si>
+    <t>flatChart</t>
+  </si>
+  <si>
+    <t>1wOl1UIGqdJg383_-c_cMTUG5yx0XgX5Z</t>
+  </si>
+  <si>
+    <t>1c6Y_hGyiTvVyhuMy44CV-ShhpyqrnZcm</t>
+  </si>
+  <si>
+    <t>1i9Dwo6yOEQYPZaDPqco4mFlGemCRZwHy</t>
+  </si>
+  <si>
+    <t>1i1LQdDPVwsK2mAMOCC1yt6hoNyQQ7wek</t>
+  </si>
+  <si>
+    <t>1iHD6GZGS2I9HpWNJOs4vcKaC2hjHuMUy</t>
+  </si>
+  <si>
+    <t>1iKWq6_Zp_It_3-0RcohzHAWGRddKo8Ts</t>
+  </si>
+  <si>
+    <t>16htn7tXBb5dWKDqBsJTeNwOLYMp34LI7</t>
+  </si>
+  <si>
+    <t>1iTjQM3aiUlwgG6_fbwrNUYpuN_ZDkmFy</t>
+  </si>
+  <si>
+    <t>1XTmCfRZFrb4plxUccn-KU3ighCjYsygO</t>
+  </si>
+  <si>
+    <t>1PoIh_SoauvSZlbEyCtSepca2Dsq8-HWY</t>
+  </si>
+  <si>
+    <t>1iLsgx_jcr8BK0rI7QSLBE1ZxSH4sv79x</t>
+  </si>
+  <si>
+    <t>1BAmtQzomAb5reMZCM9TwVlqqAPTqQezT</t>
+  </si>
+  <si>
+    <t>1rv-Fpl3VwW-bPCoDHaUNUOHr2ww5Z1wg</t>
+  </si>
+  <si>
+    <t>1KG08jfYI7haJ2fRYLg7BHwQDMA_VLf4O</t>
+  </si>
+  <si>
+    <t>15nwOf_XYXw322MH1ZJtcpMKB--5xkot_</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -133,6 +181,12 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -432,7 +486,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -569,6 +623,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -804,15 +859,17 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L979"/>
+  <dimension ref="A1:M979"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.28515625" customWidth="1"/>
     <col min="2" max="2" width="7.7109375" customWidth="1"/>
-    <col min="3" max="12" width="14.42578125" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+    <col min="4" max="12" width="14.42578125" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="59.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="49" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" s="49" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="25" t="s">
         <v>7</v>
       </c>
@@ -841,16 +898,19 @@
         <v>15</v>
       </c>
       <c r="J1" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="25" t="s">
+      <c r="L1" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="25" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M1" s="25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="34">
         <v>0</v>
       </c>
@@ -879,14 +939,17 @@
         <v>157</v>
       </c>
       <c r="J2" s="38">
-        <v>182.33333333333334</v>
+        <v>183</v>
       </c>
       <c r="K2" s="39">
         <v>4500000</v>
       </c>
       <c r="L2" s="40"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M2" s="50" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="26">
         <v>1</v>
       </c>
@@ -923,8 +986,11 @@
       <c r="L3" s="33" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M3" s="50" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="15">
         <v>1</v>
       </c>
@@ -961,8 +1027,11 @@
       <c r="L4" s="16" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M4" s="50" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="15">
         <v>1</v>
       </c>
@@ -999,8 +1068,11 @@
       <c r="L5" s="16" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M5" s="50" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17">
         <v>1</v>
       </c>
@@ -1037,8 +1109,11 @@
       <c r="L6" s="24" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M6" s="50" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>2</v>
       </c>
@@ -1075,8 +1150,11 @@
       <c r="L7" s="14" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M7" s="50" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="15">
         <v>2</v>
       </c>
@@ -1113,8 +1191,11 @@
       <c r="L8" s="16" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M8" s="50" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="15">
         <v>2</v>
       </c>
@@ -1151,8 +1232,11 @@
       <c r="L9" s="16" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M9" s="50" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17">
         <v>2</v>
       </c>
@@ -1189,8 +1273,11 @@
       <c r="L10" s="24" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M10" s="50" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <v>3</v>
       </c>
@@ -1227,8 +1314,11 @@
       <c r="L11" s="14" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M11" s="50" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="15">
         <v>3</v>
       </c>
@@ -1265,8 +1355,11 @@
       <c r="L12" s="16" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M12" s="50" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="15">
         <v>3</v>
       </c>
@@ -1303,8 +1396,11 @@
       <c r="L13" s="16" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M13" s="50" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="17">
         <v>3</v>
       </c>
@@ -1341,8 +1437,11 @@
       <c r="L14" s="24" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M14" s="50" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
         <v>4</v>
       </c>
@@ -1377,8 +1476,11 @@
         <v>2485000</v>
       </c>
       <c r="L15" s="14"/>
-    </row>
-    <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M15" s="50" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15">
         <v>4</v>
       </c>
@@ -1413,8 +1515,11 @@
         <v>2450000</v>
       </c>
       <c r="L16" s="16"/>
-    </row>
-    <row r="17" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M16" s="50" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="15">
         <v>4</v>
       </c>
@@ -1451,8 +1556,11 @@
       <c r="L17" s="16" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M17" s="50" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="17">
         <v>4</v>
       </c>
@@ -1489,8 +1597,11 @@
       <c r="L18" s="24" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M18" s="50" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7">
         <v>5</v>
       </c>
@@ -1525,8 +1636,11 @@
         <v>2525000</v>
       </c>
       <c r="L19" s="14"/>
-    </row>
-    <row r="20" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M19" s="50" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15">
         <v>5</v>
       </c>
@@ -1561,8 +1675,11 @@
         <v>2490000</v>
       </c>
       <c r="L20" s="16"/>
-    </row>
-    <row r="21" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M20" s="50" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="15">
         <v>5</v>
       </c>
@@ -1599,8 +1716,11 @@
       <c r="L21" s="16" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M21" s="50" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="17">
         <v>5</v>
       </c>
@@ -1637,8 +1757,11 @@
       <c r="L22" s="24" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M22" s="50" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7">
         <v>6</v>
       </c>
@@ -1673,8 +1796,11 @@
         <v>2565000</v>
       </c>
       <c r="L23" s="14"/>
-    </row>
-    <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M23" s="50" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15">
         <v>6</v>
       </c>
@@ -1709,8 +1835,11 @@
         <v>2530000</v>
       </c>
       <c r="L24" s="16"/>
-    </row>
-    <row r="25" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M24" s="50" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="15">
         <v>6</v>
       </c>
@@ -1745,8 +1874,11 @@
         <v>2792000</v>
       </c>
       <c r="L25" s="16"/>
-    </row>
-    <row r="26" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M25" s="50" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="17">
         <v>6</v>
       </c>
@@ -1781,8 +1913,11 @@
         <v>2504000</v>
       </c>
       <c r="L26" s="24"/>
-    </row>
-    <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M26" s="50" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7">
         <v>7</v>
       </c>
@@ -1817,8 +1952,11 @@
         <v>2605000</v>
       </c>
       <c r="L27" s="14"/>
-    </row>
-    <row r="28" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M27" s="50" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15">
         <v>7</v>
       </c>
@@ -1853,8 +1991,11 @@
         <v>2570000</v>
       </c>
       <c r="L28" s="16"/>
-    </row>
-    <row r="29" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M28" s="50" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="15">
         <v>7</v>
       </c>
@@ -1891,8 +2032,11 @@
       <c r="L29" s="16" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M29" s="50" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="41">
         <v>7</v>
       </c>
@@ -1927,8 +2071,11 @@
         <v>2592000</v>
       </c>
       <c r="L30" s="48"/>
-    </row>
-    <row r="31" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M30" s="50" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7">
         <v>8</v>
       </c>
@@ -1957,14 +2104,17 @@
         <v>55</v>
       </c>
       <c r="J31" s="12">
-        <v>138.33333333333334</v>
+        <v>139</v>
       </c>
       <c r="K31" s="13">
         <v>4200000</v>
       </c>
       <c r="L31" s="14"/>
-    </row>
-    <row r="32" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M31" s="50" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="17">
         <v>8</v>
       </c>
@@ -1999,8 +2149,11 @@
         <v>4500000</v>
       </c>
       <c r="L32" s="24"/>
-    </row>
-    <row r="33" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M32" s="50" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7">
         <v>0</v>
       </c>
@@ -2035,8 +2188,11 @@
         <v>4000000</v>
       </c>
       <c r="L33" s="14"/>
-    </row>
-    <row r="34" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M33" s="50" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="17">
         <v>0</v>
       </c>
@@ -2065,14 +2221,17 @@
         <v>187</v>
       </c>
       <c r="J34" s="22">
-        <v>147.33333333333334</v>
+        <v>148</v>
       </c>
       <c r="K34" s="23">
         <v>3900000</v>
       </c>
       <c r="L34" s="24"/>
-    </row>
-    <row r="35" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M34" s="50" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7">
         <v>1</v>
       </c>
@@ -2109,8 +2268,11 @@
       <c r="L35" s="14" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="36" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M35" s="50" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="15">
         <v>1</v>
       </c>
@@ -2147,8 +2309,11 @@
       <c r="L36" s="16" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="37" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M36" s="50" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="15">
         <v>1</v>
       </c>
@@ -2185,8 +2350,11 @@
       <c r="L37" s="16" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="38" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M37" s="50" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="17">
         <v>1</v>
       </c>
@@ -2223,8 +2391,11 @@
       <c r="L38" s="24" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="39" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M38" s="50" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7">
         <v>2</v>
       </c>
@@ -2261,8 +2432,11 @@
       <c r="L39" s="14" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="40" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M39" s="50" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="15">
         <v>2</v>
       </c>
@@ -2299,8 +2473,11 @@
       <c r="L40" s="16" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="41" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M40" s="50" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="15">
         <v>2</v>
       </c>
@@ -2337,8 +2514,11 @@
       <c r="L41" s="16" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M41" s="50" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="17">
         <v>2</v>
       </c>
@@ -2375,8 +2555,11 @@
       <c r="L42" s="24" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="43" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M42" s="50" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="7">
         <v>3</v>
       </c>
@@ -2411,8 +2594,11 @@
         <v>2648000</v>
       </c>
       <c r="L43" s="14"/>
-    </row>
-    <row r="44" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M43" s="50" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="15">
         <v>3</v>
       </c>
@@ -2447,8 +2633,11 @@
         <v>2400000</v>
       </c>
       <c r="L44" s="16"/>
-    </row>
-    <row r="45" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M44" s="50" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="15">
         <v>3</v>
       </c>
@@ -2485,8 +2674,11 @@
       <c r="L45" s="16" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="46" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M45" s="50" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="17">
         <v>3</v>
       </c>
@@ -2523,8 +2715,11 @@
       <c r="L46" s="24" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="47" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M46" s="50" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="7">
         <v>4</v>
       </c>
@@ -2559,8 +2754,11 @@
         <v>2688000</v>
       </c>
       <c r="L47" s="14"/>
-    </row>
-    <row r="48" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M47" s="50" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="15">
         <v>4</v>
       </c>
@@ -2595,8 +2793,11 @@
         <v>2440000</v>
       </c>
       <c r="L48" s="16"/>
-    </row>
-    <row r="49" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M48" s="50" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="15">
         <v>4</v>
       </c>
@@ -2633,8 +2834,11 @@
       <c r="L49" s="16" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="50" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M49" s="50" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="17">
         <v>4</v>
       </c>
@@ -2671,8 +2875,11 @@
       <c r="L50" s="24" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="51" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M50" s="50" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="7">
         <v>5</v>
       </c>
@@ -2707,8 +2914,11 @@
         <v>2728000</v>
       </c>
       <c r="L51" s="14"/>
-    </row>
-    <row r="52" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M51" s="50" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="15">
         <v>5</v>
       </c>
@@ -2743,8 +2953,11 @@
         <v>2480000</v>
       </c>
       <c r="L52" s="16"/>
-    </row>
-    <row r="53" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M52" s="50" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="15">
         <v>5</v>
       </c>
@@ -2779,8 +2992,11 @@
         <v>2567000</v>
       </c>
       <c r="L53" s="16"/>
-    </row>
-    <row r="54" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M53" s="50" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="17">
         <v>5</v>
       </c>
@@ -2817,8 +3033,11 @@
       <c r="L54" s="24" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="55" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M54" s="50" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="7">
         <v>6</v>
       </c>
@@ -2853,8 +3072,11 @@
         <v>2768000</v>
       </c>
       <c r="L55" s="14"/>
-    </row>
-    <row r="56" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M55" s="50" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="15">
         <v>6</v>
       </c>
@@ -2889,8 +3111,11 @@
         <v>2520000</v>
       </c>
       <c r="L56" s="16"/>
-    </row>
-    <row r="57" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M56" s="50" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="15">
         <v>6</v>
       </c>
@@ -2925,8 +3150,11 @@
         <v>2607000</v>
       </c>
       <c r="L57" s="16"/>
-    </row>
-    <row r="58" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M57" s="50" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="17">
         <v>6</v>
       </c>
@@ -2961,8 +3189,11 @@
         <v>2848000</v>
       </c>
       <c r="L58" s="24"/>
-    </row>
-    <row r="59" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M58" s="50" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="7">
         <v>7</v>
       </c>
@@ -2997,8 +3228,11 @@
         <v>2906000</v>
       </c>
       <c r="L59" s="14"/>
-    </row>
-    <row r="60" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M59" s="50" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="15">
         <v>7</v>
       </c>
@@ -3033,8 +3267,11 @@
         <v>2658000</v>
       </c>
       <c r="L60" s="16"/>
-    </row>
-    <row r="61" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M60" s="50" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="15">
         <v>7</v>
       </c>
@@ -3069,8 +3306,11 @@
         <v>2697000</v>
       </c>
       <c r="L61" s="16"/>
-    </row>
-    <row r="62" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M61" s="50" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="17">
         <v>7</v>
       </c>
@@ -3107,8 +3347,11 @@
       <c r="L62" s="24" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="63" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M62" s="50" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="7">
         <v>8</v>
       </c>
@@ -3137,14 +3380,17 @@
         <v>64</v>
       </c>
       <c r="J63" s="12">
-        <v>141.33333333333334</v>
+        <v>142</v>
       </c>
       <c r="K63" s="13">
         <v>4200000</v>
       </c>
       <c r="L63" s="14"/>
-    </row>
-    <row r="64" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M63" s="50" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="17">
         <v>8</v>
       </c>
@@ -3173,12 +3419,15 @@
         <v>49</v>
       </c>
       <c r="J64" s="22">
-        <v>164.33333333333334</v>
+        <v>165</v>
       </c>
       <c r="K64" s="23">
         <v>4500000</v>
       </c>
       <c r="L64" s="24"/>
+      <c r="M64" s="50" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/גדות סקיי - מחירון 46.xlsx
+++ b/גדות סקיי - מחירון 46.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Windows.old\Users\Public\VUE\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1154DF1B-A0B3-4FD3-9EAF-5AA61AB735CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A4F48F-455C-4BA9-B6B6-EED245F58B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{025406CF-A7AE-4DE8-B584-23F180A0A057}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{025406CF-A7AE-4DE8-B584-23F180A0A057}"/>
   </bookViews>
   <sheets>
     <sheet name="price" sheetId="1" r:id="rId1"/>
@@ -860,16 +860,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M979"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.28515625" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" customWidth="1"/>
-    <col min="4" max="12" width="14.42578125" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="59.28515625" customWidth="1"/>
+    <col min="1" max="1" width="8.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" customWidth="1"/>
+    <col min="3" max="12" width="14.44140625" customWidth="1"/>
+    <col min="13" max="13" width="59.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="49" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" s="49" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="25" t="s">
         <v>7</v>
       </c>
@@ -910,7 +909,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="34">
         <v>0</v>
       </c>
@@ -949,7 +948,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="26">
         <v>1</v>
       </c>
@@ -990,7 +989,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="15">
         <v>1</v>
       </c>
@@ -1031,7 +1030,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="15">
         <v>1</v>
       </c>
@@ -1072,7 +1071,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="17">
         <v>1</v>
       </c>
@@ -1113,7 +1112,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>2</v>
       </c>
@@ -1154,7 +1153,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="15">
         <v>2</v>
       </c>
@@ -1195,7 +1194,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="15">
         <v>2</v>
       </c>
@@ -1236,7 +1235,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="17">
         <v>2</v>
       </c>
@@ -1277,7 +1276,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>3</v>
       </c>
@@ -1318,7 +1317,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="15">
         <v>3</v>
       </c>
@@ -1359,7 +1358,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="15">
         <v>3</v>
       </c>
@@ -1400,7 +1399,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="17">
         <v>3</v>
       </c>
@@ -1441,7 +1440,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
         <v>4</v>
       </c>
@@ -1480,7 +1479,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15">
         <v>4</v>
       </c>
@@ -1519,7 +1518,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="15">
         <v>4</v>
       </c>
@@ -1560,7 +1559,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="17">
         <v>4</v>
       </c>
@@ -1601,7 +1600,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
         <v>5</v>
       </c>
@@ -1640,7 +1639,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15">
         <v>5</v>
       </c>
@@ -1679,7 +1678,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="15">
         <v>5</v>
       </c>
@@ -1720,7 +1719,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="17">
         <v>5</v>
       </c>
@@ -1761,7 +1760,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7">
         <v>6</v>
       </c>
@@ -1800,7 +1799,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15">
         <v>6</v>
       </c>
@@ -1839,7 +1838,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="15">
         <v>6</v>
       </c>
@@ -1878,7 +1877,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="17">
         <v>6</v>
       </c>
@@ -1917,7 +1916,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7">
         <v>7</v>
       </c>
@@ -1956,7 +1955,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15">
         <v>7</v>
       </c>
@@ -1995,7 +1994,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="15">
         <v>7</v>
       </c>
@@ -2036,7 +2035,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="41">
         <v>7</v>
       </c>
@@ -2075,7 +2074,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7">
         <v>8</v>
       </c>
@@ -2114,7 +2113,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="17">
         <v>8</v>
       </c>
@@ -2153,7 +2152,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7">
         <v>0</v>
       </c>
@@ -2192,7 +2191,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="17">
         <v>0</v>
       </c>
@@ -2231,7 +2230,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7">
         <v>1</v>
       </c>
@@ -2272,7 +2271,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="15">
         <v>1</v>
       </c>
@@ -2313,7 +2312,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="15">
         <v>1</v>
       </c>
@@ -2354,7 +2353,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="17">
         <v>1</v>
       </c>
@@ -2395,7 +2394,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7">
         <v>2</v>
       </c>
@@ -2436,7 +2435,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="15">
         <v>2</v>
       </c>
@@ -2477,7 +2476,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="15">
         <v>2</v>
       </c>
@@ -2518,7 +2517,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="17">
         <v>2</v>
       </c>
@@ -2559,7 +2558,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="7">
         <v>3</v>
       </c>
@@ -2598,7 +2597,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="15">
         <v>3</v>
       </c>
@@ -2637,7 +2636,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="15">
         <v>3</v>
       </c>
@@ -2678,7 +2677,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="17">
         <v>3</v>
       </c>
@@ -2719,7 +2718,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7">
         <v>4</v>
       </c>
@@ -2758,7 +2757,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="15">
         <v>4</v>
       </c>
@@ -2797,7 +2796,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="15">
         <v>4</v>
       </c>
@@ -2838,7 +2837,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="17">
         <v>4</v>
       </c>
@@ -2879,7 +2878,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="7">
         <v>5</v>
       </c>
@@ -2918,7 +2917,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="15">
         <v>5</v>
       </c>
@@ -2957,7 +2956,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="15">
         <v>5</v>
       </c>
@@ -2996,7 +2995,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="17">
         <v>5</v>
       </c>
@@ -3037,7 +3036,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="7">
         <v>6</v>
       </c>
@@ -3076,7 +3075,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="56" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="15">
         <v>6</v>
       </c>
@@ -3115,7 +3114,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="15">
         <v>6</v>
       </c>
@@ -3154,7 +3153,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="17">
         <v>6</v>
       </c>
@@ -3193,7 +3192,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="7">
         <v>7</v>
       </c>
@@ -3232,7 +3231,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="15">
         <v>7</v>
       </c>
@@ -3271,7 +3270,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="15">
         <v>7</v>
       </c>
@@ -3310,7 +3309,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="17">
         <v>7</v>
       </c>
@@ -3351,7 +3350,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="7">
         <v>8</v>
       </c>
@@ -3390,7 +3389,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="17">
         <v>8</v>
       </c>
@@ -3429,921 +3428,921 @@
         <v>34</v>
       </c>
     </row>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="A2:K64">
     <cfRule type="expression" dxfId="1" priority="2">
